--- a/reports/二级子公司D_现金流量表_2026-06.xlsx
+++ b/reports/二级子公司D_现金流量表_2026-06.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>44685108</v>
+        <v>43504779</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>391030848</v>
+        <v>379379603</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1472387</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>8356150</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>742626</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>4175170</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>367716</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2088589</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>297054</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>1670510</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>220853</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1252794</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>148243</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>835488</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>110718</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>626245</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>73895</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>417821</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>185120</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1043637</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>92566</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>524958</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>59002</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>331850</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>190962</v>
+        <v>184496</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1079028</v>
+        <v>1047878</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1273080</v>
+        <v>1242148</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>7193520</v>
+        <v>6983062</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>46149150</v>
+        <v>48701603</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>48801400</v>
+        <v>47416704</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>275751600</v>
+        <v>267602837</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>491614</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>2785541</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>370896</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2087348</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>245262</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1392615</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>185700</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1043875</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>122585</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>696133</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>93265</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>524762</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>7638480</v>
+        <v>7391757</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>43161120</v>
+        <v>41895703</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>4031420</v>
+        <v>3921401</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>22779480</v>
+        <v>22123014</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1591350</v>
+        <v>1544513</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>8991900</v>
+        <v>8726481</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>62062650</v>
+        <v>61783697</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>-15913500</v>
+        <v>-13082094</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>82400</v>
+        <v>79679</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>494400</v>
+        <v>480038</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>721000</v>
+        <v>699027</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>4326000</v>
+        <v>4199446</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>432600</v>
+        <v>419909</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>2595600</v>
+        <v>2520564</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>803400</v>
+        <v>778706</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8240000</v>
+        <v>7974455</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>49440000</v>
+        <v>48015868</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1236000</v>
+        <v>1205105</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>7416000</v>
+        <v>7197595</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5665000</v>
+        <v>5473215</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>33990000</v>
+        <v>33009987</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>185400</v>
+        <v>179568</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1112400</v>
+        <v>1079933</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8425400</v>
+        <v>8154023</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7622000</v>
+        <v>-7375317</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1545000</v>
+        <v>1505374</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>9270000</v>
+        <v>8996980</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2575000</v>
+        <v>2512407</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>15450000</v>
+        <v>14995722</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2575000</v>
+        <v>2487755</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>15450000</v>
+        <v>15003196</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>82400</v>
+        <v>80346</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>494400</v>
+        <v>479944</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4202400</v>
+        <v>4098127</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2060000</v>
+        <v>2003839</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>12360000</v>
+        <v>12001154</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2060000</v>
+        <v>1999308</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>12360000</v>
+        <v>11997669</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>329600</v>
+        <v>319596</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>1977600</v>
+        <v>1920521</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>288400</v>
+        <v>278899</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>1730400</v>
+        <v>1680566</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>41200</v>
+        <v>40188</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>247200</v>
+        <v>239924</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2430800</v>
+        <v>2363623</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1771600</v>
+        <v>1734504</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>-21763900</v>
+        <v>-18722907</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>-21763900</v>
+        <v>-18722907</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
